--- a/demo/leviers_demo.xlsx
+++ b/demo/leviers_demo.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Leviers" sheetId="1" r:id="rId1"/>
+    <sheet name="Sous-leviers" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -1147,4 +1148,176 @@
     <ignoredError numberStoredAsText="1" sqref="A1:AC8"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Levier Code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Nom sous-levier</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Poste de dépense</v>
+      </c>
+      <c r="D1" t="str">
+        <v>BU</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Compte P&amp;L</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Impact brut (€M)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Impact net (€M)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>AC-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Rationalisation fournisseurs packaging – Europe</v>
+      </c>
+      <c r="C2" t="str">
+        <v>COGS Packaging</v>
+      </c>
+      <c r="D2" t="str">
+        <v>BU Industrie</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Cost of Goods Sold</v>
+      </c>
+      <c r="F2">
+        <v>2.5</v>
+      </c>
+      <c r="G2">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AC-001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Rationalisation fournisseurs packaging – Asie</v>
+      </c>
+      <c r="C3" t="str">
+        <v>COGS Packaging APAC</v>
+      </c>
+      <c r="D3" t="str">
+        <v>BU Industrie</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Cost of Goods Sold</v>
+      </c>
+      <c r="F3">
+        <v>1.7</v>
+      </c>
+      <c r="G3">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AC-002</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Maintenance prédictive lignes B1-B4</v>
+      </c>
+      <c r="C4" t="str">
+        <v>COGS Maintenance</v>
+      </c>
+      <c r="D4" t="str">
+        <v>BU Industrie</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Cost of Goods Sold</v>
+      </c>
+      <c r="F4">
+        <v>2.8</v>
+      </c>
+      <c r="G4">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>AC-003</v>
+      </c>
+      <c r="B5" t="str">
+        <v>RPA processus comptables</v>
+      </c>
+      <c r="C5" t="str">
+        <v>G&amp;A Finance</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Corporate</v>
+      </c>
+      <c r="E5" t="str">
+        <v>General &amp; Admin</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>AC-003</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Automatisation déclarations TVA</v>
+      </c>
+      <c r="C6" t="str">
+        <v>G&amp;A Tax</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Corporate</v>
+      </c>
+      <c r="E6" t="str">
+        <v>General &amp; Admin</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AC-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Transfert activités Mannheim → Rotterdam</v>
+      </c>
+      <c r="C7" t="str">
+        <v>COGS Logistique EMEA</v>
+      </c>
+      <c r="D7" t="str">
+        <v>BU Industrie</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Cost of Goods Sold</v>
+      </c>
+      <c r="F7">
+        <v>2.1</v>
+      </c>
+      <c r="G7">
+        <v>1.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/demo/leviers_demo.xlsx
+++ b/demo/leviers_demo.xlsx
@@ -1152,29 +1152,86 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:S7"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" customWidth="1"/>
+    <col min="10" max="10" width="24.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Levier Code</v>
+        <v>Code levier</v>
       </c>
       <c r="B1" t="str">
         <v>Nom sous-levier</v>
       </c>
       <c r="C1" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="D1" t="str">
         <v>Poste de dépense</v>
       </c>
-      <c r="D1" t="str">
-        <v>BU</v>
-      </c>
       <c r="E1" t="str">
+        <v>Business Unit</v>
+      </c>
+      <c r="F1" t="str">
         <v>Compte P&amp;L</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Impact brut (€M)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Impact net (€M)</v>
+      </c>
+      <c r="I1" t="str">
+        <v>OPEX one-off (€M)</v>
+      </c>
+      <c r="J1" t="str">
+        <v>OPEX récurrent (€M/an)</v>
+      </c>
+      <c r="K1" t="str">
+        <v>CAPEX (€M)</v>
+      </c>
+      <c r="L1" t="str">
+        <v>ETP</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Population impactée</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Date de départ</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Date de fin</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Statut</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Priorité</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Risque</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Dépendances</v>
       </c>
     </row>
     <row r="2">
@@ -1185,19 +1242,55 @@
         <v>Rationalisation fournisseurs packaging – Europe</v>
       </c>
       <c r="C2" t="str">
+        <v>Isabelle Roy</v>
+      </c>
+      <c r="D2" t="str">
         <v>COGS Packaging</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>BU Industrie</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>Cost of Goods Sold</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>2.5</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>2.2</v>
+      </c>
+      <c r="I2">
+        <v>0.2</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.05</v>
+      </c>
+      <c r="L2">
+        <v>-2</v>
+      </c>
+      <c r="M2">
+        <v>80</v>
+      </c>
+      <c r="N2" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="O2" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="P2" t="str">
+        <v>L3 · Validé</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>high</v>
+      </c>
+      <c r="R2" t="str">
+        <v>medium</v>
+      </c>
+      <c r="S2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1208,19 +1301,55 @@
         <v>Rationalisation fournisseurs packaging – Asie</v>
       </c>
       <c r="C3" t="str">
+        <v>Isabelle Roy</v>
+      </c>
+      <c r="D3" t="str">
         <v>COGS Packaging APAC</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>BU Industrie</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Cost of Goods Sold</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1.7</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1.6</v>
+      </c>
+      <c r="I3">
+        <v>0.1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0.05</v>
+      </c>
+      <c r="L3">
+        <v>-1</v>
+      </c>
+      <c r="M3">
+        <v>40</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="O3" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="P3" t="str">
+        <v>L2 · Qualifié</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>medium</v>
+      </c>
+      <c r="R3" t="str">
+        <v>medium</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1231,19 +1360,55 @@
         <v>Maintenance prédictive lignes B1-B4</v>
       </c>
       <c r="C4" t="str">
+        <v>Thomas Petit</v>
+      </c>
+      <c r="D4" t="str">
         <v>COGS Maintenance</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>BU Industrie</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Cost of Goods Sold</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>2.8</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>2.5</v>
+      </c>
+      <c r="I4">
+        <v>0.2</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.8</v>
+      </c>
+      <c r="L4">
+        <v>-5</v>
+      </c>
+      <c r="M4">
+        <v>340</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="O4" t="str">
+        <v>2026-12-31</v>
+      </c>
+      <c r="P4" t="str">
+        <v>L4 · Planifié</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>high</v>
+      </c>
+      <c r="R4" t="str">
+        <v>high</v>
+      </c>
+      <c r="S4" t="str">
+        <v>AC-001:SS</v>
       </c>
     </row>
     <row r="5">
@@ -1254,19 +1419,55 @@
         <v>RPA processus comptables</v>
       </c>
       <c r="C5" t="str">
+        <v>Claire Bernard</v>
+      </c>
+      <c r="D5" t="str">
         <v>G&amp;A Finance</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>Corporate</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>General &amp; Admin</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.8</v>
+      </c>
+      <c r="I5">
+        <v>0.3</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.3</v>
+      </c>
+      <c r="L5">
+        <v>-2</v>
+      </c>
+      <c r="M5">
+        <v>25</v>
+      </c>
+      <c r="N5" t="str">
+        <v>2026-01-15</v>
+      </c>
+      <c r="O5" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="P5" t="str">
+        <v>L2 · Qualifié</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>medium</v>
+      </c>
+      <c r="R5" t="str">
+        <v>low</v>
+      </c>
+      <c r="S5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1277,19 +1478,55 @@
         <v>Automatisation déclarations TVA</v>
       </c>
       <c r="C6" t="str">
+        <v>Claire Bernard</v>
+      </c>
+      <c r="D6" t="str">
         <v>G&amp;A Tax</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>Corporate</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>General &amp; Admin</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.5</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.4</v>
+      </c>
+      <c r="I6">
+        <v>0.1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0.2</v>
+      </c>
+      <c r="L6">
+        <v>-2</v>
+      </c>
+      <c r="M6">
+        <v>20</v>
+      </c>
+      <c r="N6" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="O6" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="P6" t="str">
+        <v>L1 · Idée</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>medium</v>
+      </c>
+      <c r="R6" t="str">
+        <v>low</v>
+      </c>
+      <c r="S6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1300,24 +1537,60 @@
         <v>Transfert activités Mannheim → Rotterdam</v>
       </c>
       <c r="C7" t="str">
+        <v>Marc Dubois</v>
+      </c>
+      <c r="D7" t="str">
         <v>COGS Logistique EMEA</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>BU Industrie</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>Cost of Goods Sold</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>2.1</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>1.8</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1.2</v>
+      </c>
+      <c r="L7">
+        <v>-6</v>
+      </c>
+      <c r="M7">
+        <v>280</v>
+      </c>
+      <c r="N7" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="O7" t="str">
+        <v>2026-12-31</v>
+      </c>
+      <c r="P7" t="str">
+        <v>L3 · Validé</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>high</v>
+      </c>
+      <c r="R7" t="str">
+        <v>critical</v>
+      </c>
+      <c r="S7" t="str">
+        <v>AC-002:FS</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/demo/leviers_demo.xlsx
+++ b/demo/leviers_demo.xlsx
@@ -1593,4 +1593,237 @@
     <ignoredError numberStoredAsText="1" sqref="A1:S7"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F16B230D3CD39F4BAA3018F15263DE85" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5ae69f3139e7ef21b6cc103c990486d4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7fa62201-75e0-41c1-b197-21f4b9f9df04" xmlns:ns3="67d4690d-55be-4538-8d28-eed63c761cc5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7c50e1417aeafdb8d8b3d815e0063be9" ns2:_="" ns3:_="">
+    <xsd:import namespace="7fa62201-75e0-41c1-b197-21f4b9f9df04"/>
+    <xsd:import namespace="67d4690d-55be-4538-8d28-eed63c761cc5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7fa62201-75e0-41c1-b197-21f4b9f9df04" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="a8e8d813-e4e5-48d0-aeb8-e19ab3349c6b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="67d4690d-55be-4538-8d28-eed63c761cc5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a4b1418e-1abc-4596-86ca-d5530fa7bb6f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="67d4690d-55be-4538-8d28-eed63c761cc5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="67d4690d-55be-4538-8d28-eed63c761cc5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7fa62201-75e0-41c1-b197-21f4b9f9df04">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1133D46-CF6D-42C4-A4D0-D2F8136FC78A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4DC387D-5336-46BF-A331-ECB0200E7A9F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6B8ECDC-8425-4E83-9E67-12DCA9865A07}"/>
 </file>
--- a/demo/leviers_demo.xlsx
+++ b/demo/leviers_demo.xlsx
@@ -4,7 +4,8 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Leviers" sheetId="1" r:id="rId1"/>
-    <sheet name="Sous-leviers" sheetId="2" r:id="rId2"/>
+    <sheet name="Actions" sheetId="2" r:id="rId2"/>
+    <sheet name="Impacts" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,38 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC8"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="21.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="16.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
-    <col min="15" max="15" width="16.83203125" customWidth="1"/>
-    <col min="16" max="16" width="21.83203125" customWidth="1"/>
-    <col min="17" max="17" width="14.83203125" customWidth="1"/>
-    <col min="18" max="18" width="17.83203125" customWidth="1"/>
-    <col min="19" max="19" width="14.83203125" customWidth="1"/>
-    <col min="20" max="20" width="14.83203125" customWidth="1"/>
-    <col min="21" max="21" width="25.83203125" customWidth="1"/>
-    <col min="22" max="22" width="24.83203125" customWidth="1"/>
-    <col min="23" max="23" width="21.83203125" customWidth="1"/>
-    <col min="24" max="24" width="21.83203125" customWidth="1"/>
-    <col min="25" max="25" width="14.83203125" customWidth="1"/>
-    <col min="26" max="26" width="19.83203125" customWidth="1"/>
-    <col min="27" max="27" width="24.83203125" customWidth="1"/>
-    <col min="28" max="28" width="39.83203125" customWidth="1"/>
-    <col min="29" max="29" width="14.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:AB8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,78 +415,75 @@
         <v>Workstream</v>
       </c>
       <c r="E1" t="str">
+        <v>Programme</v>
+      </c>
+      <c r="F1" t="str">
         <v>Owner</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Owner (initiales)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Sponsor</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Sponsor (initiales)</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Géographie</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Pays</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Entité</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Fonction</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Centre de coût</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Compte P&amp;L impacté</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Date de départ</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Date de fin estimée</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Statut</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Progression (%)</v>
       </c>
-      <c r="S1" t="str">
-        <v>Priorité</v>
-      </c>
       <c r="T1" t="str">
-        <v>Risque</v>
+        <v>Impact estimé brut (€M)</v>
       </c>
       <c r="U1" t="str">
-        <v>Impact estimé brut (€M)</v>
+        <v>Impact estimé net (€M)</v>
       </c>
       <c r="V1" t="str">
-        <v>Impact estimé net (€M)</v>
+        <v>Impact estimé (ETP)</v>
       </c>
       <c r="W1" t="str">
-        <v>Impact estimé (ETP)</v>
+        <v>Population impactée</v>
       </c>
       <c r="X1" t="str">
-        <v>Population impactée</v>
+        <v>CAPEX (€M)</v>
       </c>
       <c r="Y1" t="str">
-        <v>CAPEX (€M)</v>
+        <v>OPEX one-off (€M)</v>
       </c>
       <c r="Z1" t="str">
-        <v>OPEX one-off (€M)</v>
+        <v>OPEX récurrent (€M/an)</v>
       </c>
       <c r="AA1" t="str">
-        <v>OPEX récurrent (€M/an)</v>
+        <v>Dépendances (ID:type, séparées par ;)</v>
       </c>
       <c r="AB1" t="str">
-        <v>Dépendances (ID:type, séparées par ;)</v>
-      </c>
-      <c r="AC1" t="str">
         <v>Description</v>
       </c>
     </row>
@@ -531,82 +498,79 @@
         <v>Regroupement fournisseurs packaging</v>
       </c>
       <c r="D2" t="str">
-        <v>Procurement Excellence</v>
+        <v>Achats &amp; Supply Chain</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>Isabelle Roy</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>IR</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>CEO Office</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>CEO</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>Europe</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>France</v>
       </c>
-      <c r="K2" t="str">
-        <v>BU Industrie</v>
-      </c>
       <c r="L2" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="M2" t="str">
         <v>Procurement</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>CC-PROC-001</v>
       </c>
-      <c r="N2" t="str">
-        <v>Cost of Goods Sold</v>
-      </c>
       <c r="O2" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P2" t="str">
         <v>2026-02-01</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>2026-09-30</v>
       </c>
-      <c r="Q2" t="str">
-        <v>L3 · Validé</v>
-      </c>
-      <c r="R2">
+      <c r="R2" t="str">
+        <v>En cours d'exécution</v>
+      </c>
+      <c r="S2">
         <v>35</v>
       </c>
-      <c r="S2" t="str">
-        <v>high</v>
-      </c>
-      <c r="T2" t="str">
-        <v>medium</v>
+      <c r="T2">
+        <v>4.2</v>
       </c>
       <c r="U2">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="V2">
-        <v>3.8</v>
+        <v>-3</v>
       </c>
       <c r="W2">
-        <v>-3</v>
+        <v>120</v>
       </c>
       <c r="X2">
-        <v>120</v>
+        <v>0.1</v>
       </c>
       <c r="Y2">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="Z2">
-        <v>0.3</v>
-      </c>
-      <c r="AA2">
         <v>0</v>
       </c>
+      <c r="AA2" t="str">
+        <v/>
+      </c>
       <c r="AB2" t="str">
-        <v/>
-      </c>
-      <c r="AC2" t="str">
-        <v>Rationalisation de la base fournisseurs packaging de 42 à 18 fournisseurs, avec mise en concurrence et standardisation des formats.</v>
+        <v>Rationalisation de la base fournisseurs packaging avec mise en concurrence et standardisation des formats.</v>
       </c>
     </row>
     <row r="3">
@@ -620,82 +584,79 @@
         <v>Réduction temps d'arrêt lignes B</v>
       </c>
       <c r="D3" t="str">
-        <v>Operational Efficiency</v>
+        <v>Excellence Opérationnelle</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>Thomas Petit</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>TP</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Directeur Industriel</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>DI</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K3" t="str">
         <v>France</v>
       </c>
-      <c r="J3" t="str">
-        <v>France</v>
-      </c>
-      <c r="K3" t="str">
-        <v>BU Industrie</v>
-      </c>
       <c r="L3" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="M3" t="str">
         <v>Operations</v>
       </c>
-      <c r="M3" t="str">
-        <v>CC-OPS-012</v>
-      </c>
       <c r="N3" t="str">
-        <v>Cost of Goods Sold</v>
+        <v>CC-OPS-001</v>
       </c>
       <c r="O3" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P3" t="str">
         <v>2026-03-15</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>2026-12-31</v>
       </c>
-      <c r="Q3" t="str">
-        <v>L4 · Planifié</v>
-      </c>
-      <c r="R3">
+      <c r="R3" t="str">
+        <v>Implémentation planifiée</v>
+      </c>
+      <c r="S3">
         <v>20</v>
       </c>
-      <c r="S3" t="str">
-        <v>high</v>
-      </c>
-      <c r="T3" t="str">
-        <v>high</v>
+      <c r="T3">
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-5</v>
+        <v>45</v>
       </c>
       <c r="X3">
-        <v>340</v>
+        <v>0.4</v>
       </c>
       <c r="Y3">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="Z3">
-        <v>0.2</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
       </c>
       <c r="AB3" t="str">
-        <v>AC-001:SS</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>Programme de maintenance prédictive sur les lignes de production B1-B4, réduction des MTTR de 35%.</v>
+        <v>Maintenance préventive et réduction des arrêts non planifiés sur les lignes de production B.</v>
       </c>
     </row>
     <row r="4">
@@ -709,82 +670,79 @@
         <v>Automatisation back-office finance</v>
       </c>
       <c r="D4" t="str">
-        <v>Digital Transformation</v>
+        <v>Digital &amp; IT</v>
       </c>
       <c r="E4" t="str">
-        <v>Claire Bernard</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>CB</v>
+        <v>Claire Fontaine</v>
       </c>
       <c r="G4" t="str">
-        <v>DSI</v>
+        <v>CF</v>
       </c>
       <c r="H4" t="str">
-        <v>DSI</v>
+        <v>CFO</v>
       </c>
       <c r="I4" t="str">
-        <v>Global</v>
+        <v>CFO</v>
       </c>
       <c r="J4" t="str">
-        <v>France</v>
+        <v>Europe</v>
       </c>
       <c r="K4" t="str">
-        <v>Corporate</v>
+        <v>Germany</v>
       </c>
       <c r="L4" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="M4" t="str">
         <v>IT</v>
       </c>
-      <c r="M4" t="str">
-        <v>CC-FIN-005</v>
-      </c>
       <c r="N4" t="str">
-        <v>General &amp; Admin</v>
+        <v>CC-GA-001</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-01-15</v>
+        <v>GA</v>
       </c>
       <c r="P4" t="str">
-        <v>2026-08-31</v>
+        <v>2026-04-01</v>
       </c>
       <c r="Q4" t="str">
-        <v>L2 · Qualifié</v>
-      </c>
-      <c r="R4">
-        <v>10</v>
-      </c>
-      <c r="S4" t="str">
-        <v>medium</v>
-      </c>
-      <c r="T4" t="str">
-        <v>low</v>
+        <v>2026-11-30</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Business case validé</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>1.6</v>
       </c>
       <c r="U4">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>-5</v>
       </c>
       <c r="W4">
-        <v>-4</v>
+        <v>20</v>
       </c>
       <c r="X4">
-        <v>45</v>
+        <v>0.6</v>
       </c>
       <c r="Y4">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="Z4">
-        <v>0.4</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
       </c>
       <c r="AB4" t="str">
-        <v/>
-      </c>
-      <c r="AC4" t="str">
-        <v>Déploiement de RPA pour les processus comptables répétitifs (rapprochements, lettrages, déclarations TVA).</v>
+        <v>RPA sur les processus de clôture comptable et de facturation fournisseurs.</v>
       </c>
     </row>
     <row r="5">
@@ -795,85 +753,82 @@
         <v>Réorganisation &amp; Effectifs</v>
       </c>
       <c r="C5" t="str">
-        <v>Fusion équipes supply chain France-Allemagne</v>
+        <v>Fusion équipes marketing France-Allemagne</v>
       </c>
       <c r="D5" t="str">
-        <v>Org &amp; Ways of Working</v>
+        <v>Marketing &amp; Ventes</v>
       </c>
       <c r="E5" t="str">
-        <v>Pierre Lefevre</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>PL</v>
+        <v>Nadia Klein</v>
       </c>
       <c r="G5" t="str">
-        <v>DRH</v>
+        <v>NK</v>
       </c>
       <c r="H5" t="str">
-        <v>DRH</v>
+        <v>CMO</v>
       </c>
       <c r="I5" t="str">
+        <v>CMO</v>
+      </c>
+      <c r="J5" t="str">
         <v>Europe</v>
       </c>
-      <c r="J5" t="str">
-        <v>France</v>
-      </c>
       <c r="K5" t="str">
-        <v>BU Industrie</v>
+        <v>Germany</v>
       </c>
       <c r="L5" t="str">
-        <v>Supply Chain</v>
+        <v>Acme Deutschland GmbH</v>
       </c>
       <c r="M5" t="str">
-        <v>CC-SC-003</v>
+        <v>Marketing</v>
       </c>
       <c r="N5" t="str">
-        <v>Selling &amp; Marketing</v>
+        <v>CC-SGA-001</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-04-01</v>
+        <v>SGA</v>
       </c>
       <c r="P5" t="str">
-        <v>2026-11-30</v>
+        <v>2026-06-01</v>
       </c>
       <c r="Q5" t="str">
-        <v>L1 · Idée</v>
-      </c>
-      <c r="R5">
+        <v>2027-01-31</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Levier identifié</v>
+      </c>
+      <c r="S5">
         <v>0</v>
       </c>
-      <c r="S5" t="str">
-        <v>medium</v>
-      </c>
-      <c r="T5" t="str">
-        <v>high</v>
+      <c r="T5">
+        <v>1.1</v>
       </c>
       <c r="U5">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>-4</v>
       </c>
       <c r="W5">
-        <v>-8</v>
+        <v>12</v>
       </c>
       <c r="X5">
-        <v>65</v>
+        <v>0.05</v>
       </c>
       <c r="Y5">
+        <v>0.1</v>
+      </c>
+      <c r="Z5">
         <v>0</v>
       </c>
-      <c r="Z5">
-        <v>0.1</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
+      <c r="AA5" t="str">
+        <v/>
       </c>
       <c r="AB5" t="str">
-        <v/>
-      </c>
-      <c r="AC5" t="str">
-        <v>Consolidation des fonctions planification et achats logistique entre les entités française et allemande.</v>
+        <v>Mutualisation des équipes marketing France et Allemagne sous un management unique.</v>
       </c>
     </row>
     <row r="6">
@@ -887,61 +842,61 @@
         <v>Revue tarifaire produits premium</v>
       </c>
       <c r="D6" t="str">
-        <v>Commercial Effectiveness</v>
+        <v>Marketing &amp; Ventes</v>
       </c>
       <c r="E6" t="str">
-        <v>Sophie Martin</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>SM</v>
+        <v>Elena Ruiz</v>
       </c>
       <c r="G6" t="str">
-        <v>Directeur Commercial</v>
+        <v>ER</v>
       </c>
       <c r="H6" t="str">
-        <v>DC</v>
+        <v>CEO Office</v>
       </c>
       <c r="I6" t="str">
-        <v>Global</v>
+        <v>CEO</v>
       </c>
       <c r="J6" t="str">
-        <v>France</v>
+        <v>Europe</v>
       </c>
       <c r="K6" t="str">
-        <v>BU Services</v>
+        <v>Spain</v>
       </c>
       <c r="L6" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="M6" t="str">
         <v>Sales</v>
       </c>
-      <c r="M6" t="str">
-        <v>CC-SALES-001</v>
-      </c>
       <c r="N6" t="str">
-        <v>Revenue</v>
+        <v>CC-SGA-002</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-02-15</v>
+        <v>REV</v>
       </c>
       <c r="P6" t="str">
-        <v>2026-06-30</v>
+        <v>2026-01-05</v>
       </c>
       <c r="Q6" t="str">
-        <v>L5 · Réalisé</v>
-      </c>
-      <c r="R6">
+        <v>2026-05-31</v>
+      </c>
+      <c r="R6" t="str">
+        <v>Valeur réalisée</v>
+      </c>
+      <c r="S6">
         <v>100</v>
       </c>
-      <c r="S6" t="str">
-        <v>critical</v>
-      </c>
-      <c r="T6" t="str">
-        <v>low</v>
+      <c r="T6">
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -950,19 +905,16 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
+      <c r="AA6" t="str">
+        <v/>
       </c>
       <c r="AB6" t="str">
-        <v/>
-      </c>
-      <c r="AC6" t="str">
-        <v>Ajustement de la politique tarifaire sur la gamme premium (+3.2% moyenne), terminé avec impact validé.</v>
+        <v>Repositionnement tarifaire de la gamme premium sur le marché ibérique.</v>
       </c>
     </row>
     <row r="7">
@@ -976,82 +928,79 @@
         <v>Optimisation réseau entrepôts EMEA</v>
       </c>
       <c r="D7" t="str">
-        <v>Supply Chain Optimization</v>
+        <v>Achats &amp; Supply Chain</v>
       </c>
       <c r="E7" t="str">
-        <v>Marc Dubois</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>MD</v>
+        <v>Ryan Cole</v>
       </c>
       <c r="G7" t="str">
-        <v>Thomas Petit</v>
+        <v>RC</v>
       </c>
       <c r="H7" t="str">
-        <v>TP</v>
+        <v>Directeur Industriel</v>
       </c>
       <c r="I7" t="str">
-        <v>Europe</v>
+        <v>DI</v>
       </c>
       <c r="J7" t="str">
-        <v>Germany</v>
+        <v>Americas</v>
       </c>
       <c r="K7" t="str">
-        <v>GmbH</v>
+        <v>USA</v>
       </c>
       <c r="L7" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="M7" t="str">
         <v>Supply Chain</v>
       </c>
-      <c r="M7" t="str">
-        <v>CC-LOG-008</v>
-      </c>
       <c r="N7" t="str">
-        <v>Cost of Goods Sold</v>
+        <v>CC-OPS-001</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-05-01</v>
+        <v>COGS</v>
       </c>
       <c r="P7" t="str">
-        <v>2026-12-31</v>
+        <v>2026-02-15</v>
       </c>
       <c r="Q7" t="str">
-        <v>L3 · Validé</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7" t="str">
-        <v>high</v>
-      </c>
-      <c r="T7" t="str">
-        <v>critical</v>
+        <v>2026-10-15</v>
+      </c>
+      <c r="R7" t="str">
+        <v>Implémentation planifiée</v>
+      </c>
+      <c r="S7">
+        <v>10</v>
+      </c>
+      <c r="T7">
+        <v>3.4</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="V7">
-        <v>1.8</v>
+        <v>-6</v>
       </c>
       <c r="W7">
-        <v>-6</v>
+        <v>35</v>
       </c>
       <c r="X7">
-        <v>280</v>
+        <v>0.5</v>
       </c>
       <c r="Y7">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Z7">
-        <v>0.5</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="AA7" t="str">
+        <v/>
       </c>
       <c r="AB7" t="str">
-        <v>AC-002:FS</v>
-      </c>
-      <c r="AC7" t="str">
-        <v>Fermeture de l'entrepôt de Mannheim et transfert des activités vers le hub de Rotterdam.</v>
+        <v>Consolidation du réseau d'entrepôts nord-américain de 5 à 3 sites.</v>
       </c>
     </row>
     <row r="8">
@@ -1062,176 +1011,116 @@
         <v>Excellence Opérationnelle</v>
       </c>
       <c r="C8" t="str">
-        <v>Programme qualité production Belgique</v>
+        <v>Programme qualité production</v>
       </c>
       <c r="D8" t="str">
-        <v>Operational Efficiency</v>
+        <v>Excellence Opérationnelle</v>
       </c>
       <c r="E8" t="str">
-        <v>Nathan Garnier</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>NG</v>
+        <v>Marc Dubois</v>
       </c>
       <c r="G8" t="str">
-        <v>Jean Dupont</v>
+        <v>MD</v>
       </c>
       <c r="H8" t="str">
-        <v>JD</v>
+        <v>Directeur Industriel</v>
       </c>
       <c r="I8" t="str">
+        <v>DI</v>
+      </c>
+      <c r="J8" t="str">
         <v>Europe</v>
       </c>
-      <c r="J8" t="str">
-        <v>Belgium</v>
-      </c>
       <c r="K8" t="str">
-        <v>NV</v>
+        <v>France</v>
       </c>
       <c r="L8" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="M8" t="str">
         <v>Operations</v>
       </c>
-      <c r="M8" t="str">
-        <v>CC-OPS-015</v>
-      </c>
       <c r="N8" t="str">
-        <v>Cost of Goods Sold</v>
+        <v>CC-OPS-001</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-06-01</v>
+        <v>COGS</v>
       </c>
       <c r="P8" t="str">
-        <v>2026-12-31</v>
+        <v>2026-05-01</v>
       </c>
       <c r="Q8" t="str">
-        <v>L2 · Qualifié</v>
-      </c>
-      <c r="R8">
-        <v>5</v>
-      </c>
-      <c r="S8" t="str">
-        <v>medium</v>
-      </c>
-      <c r="T8" t="str">
-        <v>medium</v>
+        <v>2026-12-15</v>
+      </c>
+      <c r="R8" t="str">
+        <v>Business case validé</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0.9</v>
       </c>
       <c r="U8">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V8">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>-2</v>
+        <v>15</v>
       </c>
       <c r="X8">
-        <v>90</v>
+        <v>0.15</v>
       </c>
       <c r="Y8">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="Z8">
-        <v>0.1</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>AC-001:FS</v>
       </c>
       <c r="AB8" t="str">
-        <v/>
-      </c>
-      <c r="AC8" t="str">
-        <v>Réduction du taux de rebut de 4.2% à 1.8% sur l'unité de production de Gand via Six Sigma.</v>
+        <v>Programme qualité conditionné à la fin du regroupement fournisseurs packaging (AC-001).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S7"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" customWidth="1"/>
-    <col min="10" max="10" width="24.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="21.83203125" customWidth="1"/>
-    <col min="14" max="14" width="16.83203125" customWidth="1"/>
-    <col min="15" max="15" width="14.83203125" customWidth="1"/>
-    <col min="16" max="16" width="14.83203125" customWidth="1"/>
-    <col min="17" max="17" width="14.83203125" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" customWidth="1"/>
-    <col min="19" max="19" width="14.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:G7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Code levier</v>
+        <v>Code Levier</v>
       </c>
       <c r="B1" t="str">
-        <v>Nom sous-levier</v>
+        <v>Nom de l'action</v>
       </c>
       <c r="C1" t="str">
         <v>Owner</v>
       </c>
       <c r="D1" t="str">
-        <v>Poste de dépense</v>
+        <v>Date début</v>
       </c>
       <c r="E1" t="str">
-        <v>Business Unit</v>
+        <v>Date fin</v>
       </c>
       <c r="F1" t="str">
-        <v>Compte P&amp;L</v>
+        <v>Statut</v>
       </c>
       <c r="G1" t="str">
-        <v>Impact brut (€M)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Impact net (€M)</v>
-      </c>
-      <c r="I1" t="str">
-        <v>OPEX one-off (€M)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>OPEX récurrent (€M/an)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>CAPEX (€M)</v>
-      </c>
-      <c r="L1" t="str">
-        <v>ETP</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Population impactée</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Date de départ</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Date de fin</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Statut</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Priorité</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Risque</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Dépendances</v>
+        <v>Coût (€K)</v>
       </c>
     </row>
     <row r="2">
@@ -1239,58 +1128,22 @@
         <v>AC-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Rationalisation fournisseurs packaging – Europe</v>
+        <v>Renégocier contrats fournisseurs classe A</v>
       </c>
       <c r="C2" t="str">
         <v>Isabelle Roy</v>
       </c>
       <c r="D2" t="str">
-        <v>COGS Packaging</v>
+        <v>2026-02-01</v>
       </c>
       <c r="E2" t="str">
-        <v>BU Industrie</v>
+        <v>2026-05-31</v>
       </c>
       <c r="F2" t="str">
-        <v>Cost of Goods Sold</v>
+        <v>En cours</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
-      </c>
-      <c r="H2">
-        <v>2.2</v>
-      </c>
-      <c r="I2">
-        <v>0.2</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0.05</v>
-      </c>
-      <c r="L2">
-        <v>-2</v>
-      </c>
-      <c r="M2">
-        <v>80</v>
-      </c>
-      <c r="N2" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="O2" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="P2" t="str">
-        <v>L3 · Validé</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>high</v>
-      </c>
-      <c r="R2" t="str">
-        <v>medium</v>
-      </c>
-      <c r="S2" t="str">
-        <v/>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1298,58 +1151,22 @@
         <v>AC-001</v>
       </c>
       <c r="B3" t="str">
-        <v>Rationalisation fournisseurs packaging – Asie</v>
+        <v>Standardiser formats packaging</v>
       </c>
       <c r="C3" t="str">
         <v>Isabelle Roy</v>
       </c>
       <c r="D3" t="str">
-        <v>COGS Packaging APAC</v>
+        <v>2026-06-01</v>
       </c>
       <c r="E3" t="str">
-        <v>BU Industrie</v>
+        <v>2026-09-30</v>
       </c>
       <c r="F3" t="str">
-        <v>Cost of Goods Sold</v>
+        <v>À faire</v>
       </c>
       <c r="G3">
-        <v>1.7</v>
-      </c>
-      <c r="H3">
-        <v>1.6</v>
-      </c>
-      <c r="I3">
-        <v>0.1</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0.05</v>
-      </c>
-      <c r="L3">
-        <v>-1</v>
-      </c>
-      <c r="M3">
-        <v>40</v>
-      </c>
-      <c r="N3" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="O3" t="str">
-        <v>2026-09-30</v>
-      </c>
-      <c r="P3" t="str">
-        <v>L2 · Qualifié</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>medium</v>
-      </c>
-      <c r="R3" t="str">
-        <v>medium</v>
-      </c>
-      <c r="S3" t="str">
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -1357,176 +1174,68 @@
         <v>AC-002</v>
       </c>
       <c r="B4" t="str">
-        <v>Maintenance prédictive lignes B1-B4</v>
+        <v>Diagnostic pannes lignes B</v>
       </c>
       <c r="C4" t="str">
         <v>Thomas Petit</v>
       </c>
       <c r="D4" t="str">
-        <v>COGS Maintenance</v>
+        <v>2026-03-15</v>
       </c>
       <c r="E4" t="str">
-        <v>BU Industrie</v>
+        <v>2026-05-15</v>
       </c>
       <c r="F4" t="str">
-        <v>Cost of Goods Sold</v>
+        <v>Terminé</v>
       </c>
       <c r="G4">
-        <v>2.8</v>
-      </c>
-      <c r="H4">
-        <v>2.5</v>
-      </c>
-      <c r="I4">
-        <v>0.2</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0.8</v>
-      </c>
-      <c r="L4">
-        <v>-5</v>
-      </c>
-      <c r="M4">
-        <v>340</v>
-      </c>
-      <c r="N4" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="O4" t="str">
-        <v>2026-12-31</v>
-      </c>
-      <c r="P4" t="str">
-        <v>L4 · Planifié</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>high</v>
-      </c>
-      <c r="R4" t="str">
-        <v>high</v>
-      </c>
-      <c r="S4" t="str">
-        <v>AC-001:SS</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AC-003</v>
+        <v>AC-002</v>
       </c>
       <c r="B5" t="str">
-        <v>RPA processus comptables</v>
+        <v>Déployer maintenance préventive</v>
       </c>
       <c r="C5" t="str">
-        <v>Claire Bernard</v>
+        <v>Thomas Petit</v>
       </c>
       <c r="D5" t="str">
-        <v>G&amp;A Finance</v>
+        <v>2026-05-16</v>
       </c>
       <c r="E5" t="str">
-        <v>Corporate</v>
+        <v>2026-12-31</v>
       </c>
       <c r="F5" t="str">
-        <v>General &amp; Admin</v>
+        <v>En cours</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>0.8</v>
-      </c>
-      <c r="I5">
-        <v>0.3</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0.3</v>
-      </c>
-      <c r="L5">
-        <v>-2</v>
-      </c>
-      <c r="M5">
-        <v>25</v>
-      </c>
-      <c r="N5" t="str">
-        <v>2026-01-15</v>
-      </c>
-      <c r="O5" t="str">
-        <v>2026-06-30</v>
-      </c>
-      <c r="P5" t="str">
-        <v>L2 · Qualifié</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>medium</v>
-      </c>
-      <c r="R5" t="str">
-        <v>low</v>
-      </c>
-      <c r="S5" t="str">
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AC-003</v>
+        <v>AC-006</v>
       </c>
       <c r="B6" t="str">
-        <v>Automatisation déclarations TVA</v>
+        <v>Sélection des 3 sites cibles</v>
       </c>
       <c r="C6" t="str">
-        <v>Claire Bernard</v>
+        <v>Ryan Cole</v>
       </c>
       <c r="D6" t="str">
-        <v>G&amp;A Tax</v>
+        <v>2026-02-15</v>
       </c>
       <c r="E6" t="str">
-        <v>Corporate</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F6" t="str">
-        <v>General &amp; Admin</v>
+        <v>Terminé</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
-      </c>
-      <c r="H6">
-        <v>0.4</v>
-      </c>
-      <c r="I6">
-        <v>0.1</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0.2</v>
-      </c>
-      <c r="L6">
-        <v>-2</v>
-      </c>
-      <c r="M6">
-        <v>20</v>
-      </c>
-      <c r="N6" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="O6" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="P6" t="str">
-        <v>L1 · Idée</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>medium</v>
-      </c>
-      <c r="R6" t="str">
-        <v>low</v>
-      </c>
-      <c r="S6" t="str">
-        <v/>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -1534,296 +1243,258 @@
         <v>AC-006</v>
       </c>
       <c r="B7" t="str">
-        <v>Transfert activités Mannheim → Rotterdam</v>
+        <v>Migration des flux logistiques</v>
       </c>
       <c r="C7" t="str">
-        <v>Marc Dubois</v>
+        <v>Ryan Cole</v>
       </c>
       <c r="D7" t="str">
-        <v>COGS Logistique EMEA</v>
+        <v>2026-05-01</v>
       </c>
       <c r="E7" t="str">
-        <v>BU Industrie</v>
+        <v>2026-10-15</v>
       </c>
       <c r="F7" t="str">
-        <v>Cost of Goods Sold</v>
+        <v>En cours</v>
       </c>
       <c r="G7">
-        <v>2.1</v>
-      </c>
-      <c r="H7">
-        <v>1.8</v>
-      </c>
-      <c r="I7">
-        <v>0.5</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>1.2</v>
-      </c>
-      <c r="L7">
-        <v>-6</v>
-      </c>
-      <c r="M7">
-        <v>280</v>
-      </c>
-      <c r="N7" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="O7" t="str">
-        <v>2026-12-31</v>
-      </c>
-      <c r="P7" t="str">
-        <v>L3 · Validé</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>high</v>
-      </c>
-      <c r="R7" t="str">
-        <v>critical</v>
-      </c>
-      <c r="S7" t="str">
-        <v>AC-002:FS</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F16B230D3CD39F4BAA3018F15263DE85" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="5ae69f3139e7ef21b6cc103c990486d4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7fa62201-75e0-41c1-b197-21f4b9f9df04" xmlns:ns3="67d4690d-55be-4538-8d28-eed63c761cc5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7c50e1417aeafdb8d8b3d815e0063be9" ns2:_="" ns3:_="">
-    <xsd:import namespace="7fa62201-75e0-41c1-b197-21f4b9f9df04"/>
-    <xsd:import namespace="67d4690d-55be-4538-8d28-eed63c761cc5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7fa62201-75e0-41c1-b197-21f4b9f9df04" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="a8e8d813-e4e5-48d0-aeb8-e19ab3349c6b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="67d4690d-55be-4538-8d28-eed63c761cc5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a4b1418e-1abc-4596-86ca-d5530fa7bb6f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="67d4690d-55be-4538-8d28-eed63c761cc5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="67d4690d-55be-4538-8d28-eed63c761cc5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7fa62201-75e0-41c1-b197-21f4b9f9df04">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1133D46-CF6D-42C4-A4D0-D2F8136FC78A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4DC387D-5336-46BF-A331-ECB0200E7A9F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6B8ECDC-8425-4E83-9E67-12DCA9865A07}"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Code Levier</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Nom de l'action</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Nature</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Montant (€M)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ETP</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Type de gain</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Date CAPEX</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Date gain</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Reconnaissance</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Poste de coût</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Centre de coût</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Entité P&amp;L</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Commentaire</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>AC-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Renégocier contrats fournisseurs classe A</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Gain</v>
+      </c>
+      <c r="D2" t="str">
+        <v>OPEX récurrent</v>
+      </c>
+      <c r="E2">
+        <v>2.2</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>Réduction de coût</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Lissé</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>CC-PROC-001</v>
+      </c>
+      <c r="M2" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AC-001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Standardiser formats packaging</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Coût</v>
+      </c>
+      <c r="D3" t="str">
+        <v>One-off</v>
+      </c>
+      <c r="E3">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>CC-PROC-001</v>
+      </c>
+      <c r="M3" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AC-002</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Déployer maintenance préventive</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Gain</v>
+      </c>
+      <c r="D4" t="str">
+        <v>OPEX récurrent</v>
+      </c>
+      <c r="E4">
+        <v>2.8</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>Réduction de coût</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Lissé</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>CC-OPS-001</v>
+      </c>
+      <c r="M4" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>AC-006</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Migration des flux logistiques</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Gain</v>
+      </c>
+      <c r="D5" t="str">
+        <v>OPEX récurrent</v>
+      </c>
+      <c r="E5">
+        <v>3.4</v>
+      </c>
+      <c r="F5" t="str">
+        <v>-6</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Réduction de coût</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Lissé</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>CC-OPS-001</v>
+      </c>
+      <c r="M5" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/demo/leviers_demo.xlsx
+++ b/demo/leviers_demo.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB8"/>
+  <dimension ref="A1:AB31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -495,7 +495,7 @@
         <v>Sourcing &amp; Achats</v>
       </c>
       <c r="C2" t="str">
-        <v>Regroupement fournisseurs packaging</v>
+        <v>Regroupement fournisseurs Europe</v>
       </c>
       <c r="D2" t="str">
         <v>Achats &amp; Supply Chain</v>
@@ -534,43 +534,43 @@
         <v>COGS</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-02-01</v>
+        <v>2026-01-01</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-09-30</v>
+        <v>2026-06-28</v>
       </c>
       <c r="R2" t="str">
-        <v>En cours d'exécution</v>
+        <v>Levier identifié</v>
       </c>
       <c r="S2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>4.2</v>
+        <v>0.67</v>
       </c>
       <c r="U2">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="V2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1</v>
+        <v>0.07</v>
       </c>
       <c r="Y2">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AA2" t="str">
         <v/>
       </c>
       <c r="AB2" t="str">
-        <v>Rationalisation de la base fournisseurs packaging avec mise en concurrence et standardisation des formats.</v>
+        <v>Levier de démo généré (sourcing &amp; achats, France).</v>
       </c>
     </row>
     <row r="3">
@@ -581,7 +581,7 @@
         <v>Excellence Opérationnelle</v>
       </c>
       <c r="C3" t="str">
-        <v>Réduction temps d'arrêt lignes B</v>
+        <v>Réduction temps d'arrêt France</v>
       </c>
       <c r="D3" t="str">
         <v>Excellence Opérationnelle</v>
@@ -605,10 +605,10 @@
         <v>Europe</v>
       </c>
       <c r="K3" t="str">
-        <v>France</v>
+        <v>Germany</v>
       </c>
       <c r="L3" t="str">
-        <v>Acme France SAS</v>
+        <v>Acme Deutschland GmbH</v>
       </c>
       <c r="M3" t="str">
         <v>Operations</v>
@@ -620,43 +620,43 @@
         <v>COGS</v>
       </c>
       <c r="P3" t="str">
-        <v>2026-03-15</v>
+        <v>2026-02-01</v>
       </c>
       <c r="Q3" t="str">
-        <v>2026-12-31</v>
+        <v>2026-08-28</v>
       </c>
       <c r="R3" t="str">
-        <v>Implémentation planifiée</v>
+        <v>Business case validé</v>
       </c>
       <c r="S3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>1.18</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>1.05</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="W3">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="X3">
-        <v>0.4</v>
+        <v>0.13</v>
       </c>
       <c r="Y3">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="Z3">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="AA3" t="str">
         <v/>
       </c>
       <c r="AB3" t="str">
-        <v>Maintenance préventive et réduction des arrêts non planifiés sur les lignes de production B.</v>
+        <v>Levier de démo généré (excellence opérationnelle, Germany).</v>
       </c>
     </row>
     <row r="4">
@@ -667,7 +667,7 @@
         <v>Digitalisation &amp; Automatisation</v>
       </c>
       <c r="C4" t="str">
-        <v>Automatisation back-office finance</v>
+        <v>Automatisation back-office Allemagne</v>
       </c>
       <c r="D4" t="str">
         <v>Digital &amp; IT</v>
@@ -691,10 +691,10 @@
         <v>Europe</v>
       </c>
       <c r="K4" t="str">
-        <v>Germany</v>
+        <v>Spain</v>
       </c>
       <c r="L4" t="str">
-        <v>Acme Deutschland GmbH</v>
+        <v>Acme Iberia SL</v>
       </c>
       <c r="M4" t="str">
         <v>IT</v>
@@ -706,43 +706,43 @@
         <v>GA</v>
       </c>
       <c r="P4" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="Q4" t="str">
-        <v>2026-11-30</v>
+        <v>2026-10-28</v>
       </c>
       <c r="R4" t="str">
-        <v>Business case validé</v>
+        <v>Implémentation planifiée</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T4">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="U4">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V4">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="W4">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="X4">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
       <c r="Y4">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="Z4">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AA4" t="str">
-        <v/>
+        <v>AC-002:FF</v>
       </c>
       <c r="AB4" t="str">
-        <v>RPA sur les processus de clôture comptable et de facturation fournisseurs.</v>
+        <v>Levier de démo généré (digitalisation &amp; automatisation, Spain).</v>
       </c>
     </row>
     <row r="5">
@@ -750,10 +750,10 @@
         <v>AC-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Réorganisation &amp; Effectifs</v>
+        <v>Pricing &amp; Revenue Management</v>
       </c>
       <c r="C5" t="str">
-        <v>Fusion équipes marketing France-Allemagne</v>
+        <v>Fusion équipes Espagne</v>
       </c>
       <c r="D5" t="str">
         <v>Marketing &amp; Ventes</v>
@@ -774,61 +774,61 @@
         <v>CMO</v>
       </c>
       <c r="J5" t="str">
-        <v>Europe</v>
+        <v>Americas</v>
       </c>
       <c r="K5" t="str">
-        <v>Germany</v>
+        <v>USA</v>
       </c>
       <c r="L5" t="str">
-        <v>Acme Deutschland GmbH</v>
+        <v>Acme USA Inc.</v>
       </c>
       <c r="M5" t="str">
-        <v>Marketing</v>
+        <v>Sales</v>
       </c>
       <c r="N5" t="str">
-        <v>CC-SGA-001</v>
+        <v>CC-SGA-002</v>
       </c>
       <c r="O5" t="str">
-        <v>SGA</v>
+        <v>REV</v>
       </c>
       <c r="P5" t="str">
-        <v>2026-06-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="Q5" t="str">
-        <v>2027-01-31</v>
+        <v>2026-12-28</v>
       </c>
       <c r="R5" t="str">
-        <v>Levier identifié</v>
+        <v>En cours d'exécution</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="T5">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
-        <v>0.9</v>
+        <v>1.95</v>
       </c>
       <c r="V5">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="W5">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="X5">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="Y5">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AA5" t="str">
         <v/>
       </c>
       <c r="AB5" t="str">
-        <v>Mutualisation des équipes marketing France et Allemagne sous un management unique.</v>
+        <v>Levier de démo généré (pricing &amp; revenue management, USA).</v>
       </c>
     </row>
     <row r="6">
@@ -836,10 +836,10 @@
         <v>AC-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Pricing &amp; Revenue Management</v>
+        <v>Réorganisation &amp; Effectifs</v>
       </c>
       <c r="C6" t="str">
-        <v>Revue tarifaire produits premium</v>
+        <v>Revue tarifaire US</v>
       </c>
       <c r="D6" t="str">
         <v>Marketing &amp; Ventes</v>
@@ -854,34 +854,34 @@
         <v>ER</v>
       </c>
       <c r="H6" t="str">
-        <v>CEO Office</v>
+        <v>Directeur Commercial</v>
       </c>
       <c r="I6" t="str">
-        <v>CEO</v>
+        <v>DC</v>
       </c>
       <c r="J6" t="str">
         <v>Europe</v>
       </c>
       <c r="K6" t="str">
-        <v>Spain</v>
+        <v>France</v>
       </c>
       <c r="L6" t="str">
-        <v>Acme Iberia SL</v>
+        <v>Acme France SAS</v>
       </c>
       <c r="M6" t="str">
-        <v>Sales</v>
+        <v>Marketing</v>
       </c>
       <c r="N6" t="str">
-        <v>CC-SGA-002</v>
+        <v>CC-SGA-001</v>
       </c>
       <c r="O6" t="str">
-        <v>REV</v>
+        <v>SGA</v>
       </c>
       <c r="P6" t="str">
-        <v>2026-01-05</v>
+        <v>2026-05-01</v>
       </c>
       <c r="Q6" t="str">
-        <v>2026-05-31</v>
+        <v>2027-02-28</v>
       </c>
       <c r="R6" t="str">
         <v>Valeur réalisée</v>
@@ -890,10 +890,10 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>2.69</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -902,19 +902,19 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="Y6">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AA6" t="str">
-        <v/>
+        <v>AC-004:FS</v>
       </c>
       <c r="AB6" t="str">
-        <v>Repositionnement tarifaire de la gamme premium sur le marché ibérique.</v>
+        <v>Levier de démo généré (réorganisation &amp; effectifs, France).</v>
       </c>
     </row>
     <row r="7">
@@ -925,7 +925,7 @@
         <v>Supply Chain &amp; Logistique</v>
       </c>
       <c r="C7" t="str">
-        <v>Optimisation réseau entrepôts EMEA</v>
+        <v>Optimisation réseau EMEA</v>
       </c>
       <c r="D7" t="str">
         <v>Achats &amp; Supply Chain</v>
@@ -940,19 +940,19 @@
         <v>RC</v>
       </c>
       <c r="H7" t="str">
-        <v>Directeur Industriel</v>
+        <v>Directrice RH</v>
       </c>
       <c r="I7" t="str">
-        <v>DI</v>
+        <v>DRH</v>
       </c>
       <c r="J7" t="str">
-        <v>Americas</v>
+        <v>Europe</v>
       </c>
       <c r="K7" t="str">
-        <v>USA</v>
+        <v>Germany</v>
       </c>
       <c r="L7" t="str">
-        <v>Acme USA Inc.</v>
+        <v>Acme Deutschland GmbH</v>
       </c>
       <c r="M7" t="str">
         <v>Supply Chain</v>
@@ -964,43 +964,43 @@
         <v>COGS</v>
       </c>
       <c r="P7" t="str">
-        <v>2026-02-15</v>
+        <v>2026-06-01</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-10-15</v>
+        <v>2027-04-28</v>
       </c>
       <c r="R7" t="str">
-        <v>Implémentation planifiée</v>
+        <v>Levier identifié</v>
       </c>
       <c r="S7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="U7">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="V7">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="W7">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="X7">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="Y7">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="Z7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AA7" t="str">
-        <v/>
+        <v>AC-004:SS</v>
       </c>
       <c r="AB7" t="str">
-        <v>Consolidation du réseau d'entrepôts nord-américain de 5 à 3 sites.</v>
+        <v>Levier de démo généré (supply chain &amp; logistique, Germany).</v>
       </c>
     </row>
     <row r="8">
@@ -1008,13 +1008,13 @@
         <v>AC-007</v>
       </c>
       <c r="B8" t="str">
-        <v>Excellence Opérationnelle</v>
+        <v>Digitalisation &amp; Automatisation</v>
       </c>
       <c r="C8" t="str">
-        <v>Programme qualité production</v>
+        <v>Programme qualité Nord</v>
       </c>
       <c r="D8" t="str">
-        <v>Excellence Opérationnelle</v>
+        <v>Finance &amp; Contrôle de gestion</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1026,34 +1026,34 @@
         <v>MD</v>
       </c>
       <c r="H8" t="str">
-        <v>Directeur Industriel</v>
+        <v>CEO Office</v>
       </c>
       <c r="I8" t="str">
-        <v>DI</v>
+        <v>CEO</v>
       </c>
       <c r="J8" t="str">
         <v>Europe</v>
       </c>
       <c r="K8" t="str">
-        <v>France</v>
+        <v>Spain</v>
       </c>
       <c r="L8" t="str">
-        <v>Acme France SAS</v>
+        <v>Acme Iberia SL</v>
       </c>
       <c r="M8" t="str">
-        <v>Operations</v>
+        <v>Finance</v>
       </c>
       <c r="N8" t="str">
-        <v>CC-OPS-001</v>
+        <v>CC-GA-002</v>
       </c>
       <c r="O8" t="str">
-        <v>COGS</v>
+        <v>GA</v>
       </c>
       <c r="P8" t="str">
-        <v>2026-05-01</v>
+        <v>2026-07-01</v>
       </c>
       <c r="Q8" t="str">
-        <v>2026-12-15</v>
+        <v>2027-06-28</v>
       </c>
       <c r="R8" t="str">
         <v>Business case validé</v>
@@ -1062,36 +1062,2014 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="U8">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="V8">
+        <v>-3</v>
+      </c>
+      <c r="W8">
+        <v>24</v>
+      </c>
+      <c r="X8">
+        <v>0.4</v>
+      </c>
+      <c r="Y8">
+        <v>0.26</v>
+      </c>
+      <c r="Z8">
+        <v>0.07</v>
+      </c>
+      <c r="AA8" t="str">
+        <v/>
+      </c>
+      <c r="AB8" t="str">
+        <v>Levier de démo généré (digitalisation &amp; automatisation, Spain).</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AC-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Réorganisation &amp; Effectifs</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Renégociation baux Sud</v>
+      </c>
+      <c r="D9" t="str">
+        <v>RH &amp; Organisation</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>Léa Moreau</v>
+      </c>
+      <c r="G9" t="str">
+        <v>LM</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Directeur Industriel</v>
+      </c>
+      <c r="I9" t="str">
+        <v>DI</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="K9" t="str">
+        <v>USA</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="M9" t="str">
+        <v>HR</v>
+      </c>
+      <c r="N9" t="str">
+        <v>CC-GA-002</v>
+      </c>
+      <c r="O9" t="str">
+        <v>GA</v>
+      </c>
+      <c r="P9" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>2027-08-28</v>
+      </c>
+      <c r="R9" t="str">
+        <v>Implémentation planifiée</v>
+      </c>
+      <c r="S9">
+        <v>10</v>
+      </c>
+      <c r="T9">
+        <v>4.2</v>
+      </c>
+      <c r="U9">
+        <v>3.75</v>
+      </c>
+      <c r="V9">
+        <v>-4</v>
+      </c>
+      <c r="W9">
+        <v>36</v>
+      </c>
+      <c r="X9">
+        <v>0.45</v>
+      </c>
+      <c r="Y9">
+        <v>0.3</v>
+      </c>
+      <c r="Z9">
+        <v>0.08</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>AC-006:SF</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>Levier de démo généré (réorganisation &amp; effectifs, USA).</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AC-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Sourcing &amp; Achats</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Centralisation achats indirects Groupe</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Achats &amp; Supply Chain</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>Julien Blanc</v>
+      </c>
+      <c r="G10" t="str">
+        <v>JB</v>
+      </c>
+      <c r="H10" t="str">
+        <v>CFO</v>
+      </c>
+      <c r="I10" t="str">
+        <v>CFO</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K10" t="str">
+        <v>France</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="N10" t="str">
+        <v>CC-PROC-001</v>
+      </c>
+      <c r="O10" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P10" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="R10" t="str">
+        <v>En cours d'exécution</v>
+      </c>
+      <c r="S10">
+        <v>45</v>
+      </c>
+      <c r="T10">
+        <v>4.7</v>
+      </c>
+      <c r="U10">
+        <v>4.2</v>
+      </c>
+      <c r="V10">
         <v>0</v>
       </c>
-      <c r="W8">
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0.5</v>
+      </c>
+      <c r="Y10">
+        <v>0.34</v>
+      </c>
+      <c r="Z10">
+        <v>0.08</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>AC-008:FS;AC-004:FF</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>Levier de démo généré (sourcing &amp; achats, France).</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AC-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Excellence Opérationnelle</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Digitalisation reporting Retail</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Excellence Opérationnelle</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="G11" t="str">
+        <v>SA</v>
+      </c>
+      <c r="H11" t="str">
+        <v>CMO</v>
+      </c>
+      <c r="I11" t="str">
+        <v>CMO</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="N11" t="str">
+        <v>CC-OPS-001</v>
+      </c>
+      <c r="O11" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P11" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="R11" t="str">
+        <v>Valeur réalisée</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
+        <v>0.67</v>
+      </c>
+      <c r="U11">
+        <v>0.6</v>
+      </c>
+      <c r="V11">
+        <v>-6</v>
+      </c>
+      <c r="W11">
+        <v>42</v>
+      </c>
+      <c r="X11">
+        <v>0.07</v>
+      </c>
+      <c r="Y11">
+        <v>0.05</v>
+      </c>
+      <c r="Z11">
+        <v>0.01</v>
+      </c>
+      <c r="AA11" t="str">
+        <v/>
+      </c>
+      <c r="AB11" t="str">
+        <v>Levier de démo généré (excellence opérationnelle, Germany).</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AC-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Digitalisation &amp; Automatisation</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Rationalisation gamme Europe</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Digital &amp; IT</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>Henrik Dahl</v>
+      </c>
+      <c r="G12" t="str">
+        <v>HD</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Directeur Commercial</v>
+      </c>
+      <c r="I12" t="str">
+        <v>DC</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="M12" t="str">
+        <v>IT</v>
+      </c>
+      <c r="N12" t="str">
+        <v>CC-GA-001</v>
+      </c>
+      <c r="O12" t="str">
+        <v>GA</v>
+      </c>
+      <c r="P12" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="R12" t="str">
+        <v>Levier identifié</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>1.18</v>
+      </c>
+      <c r="U12">
+        <v>1.05</v>
+      </c>
+      <c r="V12">
+        <v>-2</v>
+      </c>
+      <c r="W12">
+        <v>16</v>
+      </c>
+      <c r="X12">
+        <v>0.13</v>
+      </c>
+      <c r="Y12">
+        <v>0.08</v>
+      </c>
+      <c r="Z12">
+        <v>0.02</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>AC-010:FF</v>
+      </c>
+      <c r="AB12" t="str">
+        <v>Levier de démo généré (digitalisation &amp; automatisation, Spain).</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>AC-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Pricing &amp; Revenue Management</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Mutualisation flotte France</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Marketing &amp; Ventes</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>Camille Vasseur</v>
+      </c>
+      <c r="G13" t="str">
+        <v>CV</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Directrice RH</v>
+      </c>
+      <c r="I13" t="str">
+        <v>DRH</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="K13" t="str">
+        <v>USA</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="N13" t="str">
+        <v>CC-SGA-002</v>
+      </c>
+      <c r="O13" t="str">
+        <v>REV</v>
+      </c>
+      <c r="P13" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="R13" t="str">
+        <v>Business case validé</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>1.68</v>
+      </c>
+      <c r="U13">
+        <v>1.5</v>
+      </c>
+      <c r="V13">
+        <v>-3</v>
+      </c>
+      <c r="W13">
+        <v>27</v>
+      </c>
+      <c r="X13">
+        <v>0.18</v>
+      </c>
+      <c r="Y13">
+        <v>0.12</v>
+      </c>
+      <c r="Z13">
+        <v>0.03</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>AC-010:SF</v>
+      </c>
+      <c r="AB13" t="str">
+        <v>Levier de démo généré (pricing &amp; revenue management, USA).</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AC-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Réorganisation &amp; Effectifs</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Automatisation support client Allemagne</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Marketing &amp; Ventes</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>Isabelle Roy</v>
+      </c>
+      <c r="G14" t="str">
+        <v>IR</v>
+      </c>
+      <c r="H14" t="str">
+        <v>CEO Office</v>
+      </c>
+      <c r="I14" t="str">
+        <v>CEO</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K14" t="str">
+        <v>France</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="N14" t="str">
+        <v>CC-SGA-001</v>
+      </c>
+      <c r="O14" t="str">
+        <v>SGA</v>
+      </c>
+      <c r="P14" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>2026-12-28</v>
+      </c>
+      <c r="R14" t="str">
+        <v>Implémentation planifiée</v>
+      </c>
+      <c r="S14">
+        <v>5</v>
+      </c>
+      <c r="T14">
+        <v>2.18</v>
+      </c>
+      <c r="U14">
+        <v>1.95</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0.23</v>
+      </c>
+      <c r="Y14">
+        <v>0.16</v>
+      </c>
+      <c r="Z14">
+        <v>0.04</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>AC-008:FF</v>
+      </c>
+      <c r="AB14" t="str">
+        <v>Levier de démo généré (réorganisation &amp; effectifs, France).</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>AC-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Supply Chain &amp; Logistique</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Optimisation stocks Espagne</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Achats &amp; Supply Chain</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>Thomas Petit</v>
+      </c>
+      <c r="G15" t="str">
+        <v>TP</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Directeur Industriel</v>
+      </c>
+      <c r="I15" t="str">
+        <v>DI</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="N15" t="str">
+        <v>CC-OPS-001</v>
+      </c>
+      <c r="O15" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P15" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="R15" t="str">
+        <v>En cours d'exécution</v>
+      </c>
+      <c r="S15">
+        <v>35</v>
+      </c>
+      <c r="T15">
+        <v>2.69</v>
+      </c>
+      <c r="U15">
+        <v>2.4</v>
+      </c>
+      <c r="V15">
+        <v>-5</v>
+      </c>
+      <c r="W15">
+        <v>35</v>
+      </c>
+      <c r="X15">
+        <v>0.29</v>
+      </c>
+      <c r="Y15">
+        <v>0.19</v>
+      </c>
+      <c r="Z15">
+        <v>0.05</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>AC-012:SS</v>
+      </c>
+      <c r="AB15" t="str">
+        <v>Levier de démo généré (supply chain &amp; logistique, Germany).</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>AC-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Digitalisation &amp; Automatisation</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Réorganisation service client US</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Finance &amp; Contrôle de gestion</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>Claire Fontaine</v>
+      </c>
+      <c r="G16" t="str">
+        <v>CF</v>
+      </c>
+      <c r="H16" t="str">
+        <v>CFO</v>
+      </c>
+      <c r="I16" t="str">
+        <v>CFO</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="N16" t="str">
+        <v>CC-GA-002</v>
+      </c>
+      <c r="O16" t="str">
+        <v>GA</v>
+      </c>
+      <c r="P16" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="R16" t="str">
+        <v>Valeur réalisée</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
+        <v>3.19</v>
+      </c>
+      <c r="U16">
+        <v>2.85</v>
+      </c>
+      <c r="V16">
+        <v>-6</v>
+      </c>
+      <c r="W16">
+        <v>48</v>
+      </c>
+      <c r="X16">
+        <v>0.34</v>
+      </c>
+      <c r="Y16">
+        <v>0.23</v>
+      </c>
+      <c r="Z16">
+        <v>0.06</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>AC-014:FF</v>
+      </c>
+      <c r="AB16" t="str">
+        <v>Levier de démo généré (digitalisation &amp; automatisation, Spain).</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>AC-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Réorganisation &amp; Effectifs</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Regroupement fournisseurs EMEA</v>
+      </c>
+      <c r="D17" t="str">
+        <v>RH &amp; Organisation</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>Nadia Klein</v>
+      </c>
+      <c r="G17" t="str">
+        <v>NK</v>
+      </c>
+      <c r="H17" t="str">
+        <v>CMO</v>
+      </c>
+      <c r="I17" t="str">
+        <v>CMO</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="K17" t="str">
+        <v>USA</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="M17" t="str">
+        <v>HR</v>
+      </c>
+      <c r="N17" t="str">
+        <v>CC-GA-002</v>
+      </c>
+      <c r="O17" t="str">
+        <v>GA</v>
+      </c>
+      <c r="P17" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>2027-06-28</v>
+      </c>
+      <c r="R17" t="str">
+        <v>Levier identifié</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>3.7</v>
+      </c>
+      <c r="U17">
+        <v>3.3</v>
+      </c>
+      <c r="V17">
+        <v>-2</v>
+      </c>
+      <c r="W17">
+        <v>18</v>
+      </c>
+      <c r="X17">
+        <v>0.4</v>
+      </c>
+      <c r="Y17">
+        <v>0.26</v>
+      </c>
+      <c r="Z17">
+        <v>0.07</v>
+      </c>
+      <c r="AA17" t="str">
+        <v/>
+      </c>
+      <c r="AB17" t="str">
+        <v>Levier de démo généré (réorganisation &amp; effectifs, USA).</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>AC-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Sourcing &amp; Achats</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Réduction temps d'arrêt Nord</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Achats &amp; Supply Chain</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>Elena Ruiz</v>
+      </c>
+      <c r="G18" t="str">
+        <v>ER</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Directeur Commercial</v>
+      </c>
+      <c r="I18" t="str">
+        <v>DC</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K18" t="str">
+        <v>France</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="N18" t="str">
+        <v>CC-PROC-001</v>
+      </c>
+      <c r="O18" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P18" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>2026-12-28</v>
+      </c>
+      <c r="R18" t="str">
+        <v>Business case validé</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>4.2</v>
+      </c>
+      <c r="U18">
+        <v>3.75</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0.45</v>
+      </c>
+      <c r="Y18">
+        <v>0.3</v>
+      </c>
+      <c r="Z18">
+        <v>0.08</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>AC-016:FS;AC-012:FF</v>
+      </c>
+      <c r="AB18" t="str">
+        <v>Levier de démo généré (sourcing &amp; achats, France).</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>AC-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Excellence Opérationnelle</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Automatisation back-office Sud</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Excellence Opérationnelle</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>Ryan Cole</v>
+      </c>
+      <c r="G19" t="str">
+        <v>RC</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Directrice RH</v>
+      </c>
+      <c r="I19" t="str">
+        <v>DRH</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="N19" t="str">
+        <v>CC-OPS-001</v>
+      </c>
+      <c r="O19" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P19" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="R19" t="str">
+        <v>Implémentation planifiée</v>
+      </c>
+      <c r="S19">
         <v>15</v>
       </c>
-      <c r="X8">
-        <v>0.15</v>
-      </c>
-      <c r="Y8">
+      <c r="T19">
+        <v>4.7</v>
+      </c>
+      <c r="U19">
+        <v>4.2</v>
+      </c>
+      <c r="V19">
+        <v>-4</v>
+      </c>
+      <c r="W19">
+        <v>28</v>
+      </c>
+      <c r="X19">
+        <v>0.5</v>
+      </c>
+      <c r="Y19">
+        <v>0.34</v>
+      </c>
+      <c r="Z19">
+        <v>0.08</v>
+      </c>
+      <c r="AA19" t="str">
+        <v>AC-016:SS</v>
+      </c>
+      <c r="AB19" t="str">
+        <v>Levier de démo généré (excellence opérationnelle, Germany).</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>AC-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Digitalisation &amp; Automatisation</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Fusion équipes Groupe</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Digital &amp; IT</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>Marc Dubois</v>
+      </c>
+      <c r="G20" t="str">
+        <v>MD</v>
+      </c>
+      <c r="H20" t="str">
+        <v>CEO Office</v>
+      </c>
+      <c r="I20" t="str">
+        <v>CEO</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="M20" t="str">
+        <v>IT</v>
+      </c>
+      <c r="N20" t="str">
+        <v>CC-GA-001</v>
+      </c>
+      <c r="O20" t="str">
+        <v>GA</v>
+      </c>
+      <c r="P20" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="R20" t="str">
+        <v>En cours d'exécution</v>
+      </c>
+      <c r="S20">
+        <v>25</v>
+      </c>
+      <c r="T20">
+        <v>0.67</v>
+      </c>
+      <c r="U20">
+        <v>0.6</v>
+      </c>
+      <c r="V20">
+        <v>-5</v>
+      </c>
+      <c r="W20">
+        <v>40</v>
+      </c>
+      <c r="X20">
+        <v>0.07</v>
+      </c>
+      <c r="Y20">
         <v>0.05</v>
       </c>
-      <c r="Z8">
+      <c r="Z20">
+        <v>0.01</v>
+      </c>
+      <c r="AA20" t="str">
+        <v/>
+      </c>
+      <c r="AB20" t="str">
+        <v>Levier de démo généré (digitalisation &amp; automatisation, Spain).</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>AC-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Pricing &amp; Revenue Management</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Revue tarifaire Retail</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Marketing &amp; Ventes</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>Léa Moreau</v>
+      </c>
+      <c r="G21" t="str">
+        <v>LM</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Directeur Industriel</v>
+      </c>
+      <c r="I21" t="str">
+        <v>DI</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="K21" t="str">
+        <v>USA</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="N21" t="str">
+        <v>CC-SGA-002</v>
+      </c>
+      <c r="O21" t="str">
+        <v>REV</v>
+      </c>
+      <c r="P21" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>2027-06-28</v>
+      </c>
+      <c r="R21" t="str">
+        <v>Valeur réalisée</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
+        <v>1.18</v>
+      </c>
+      <c r="U21">
+        <v>1.05</v>
+      </c>
+      <c r="V21">
+        <v>-6</v>
+      </c>
+      <c r="W21">
+        <v>54</v>
+      </c>
+      <c r="X21">
+        <v>0.13</v>
+      </c>
+      <c r="Y21">
+        <v>0.08</v>
+      </c>
+      <c r="Z21">
         <v>0.02</v>
       </c>
-      <c r="AA8" t="str">
-        <v>AC-001:FS</v>
-      </c>
-      <c r="AB8" t="str">
-        <v>Programme qualité conditionné à la fin du regroupement fournisseurs packaging (AC-001).</v>
+      <c r="AA21" t="str">
+        <v>AC-018:SF</v>
+      </c>
+      <c r="AB21" t="str">
+        <v>Levier de démo généré (pricing &amp; revenue management, USA).</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>AC-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Réorganisation &amp; Effectifs</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Optimisation réseau Europe</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Marketing &amp; Ventes</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>Julien Blanc</v>
+      </c>
+      <c r="G22" t="str">
+        <v>JB</v>
+      </c>
+      <c r="H22" t="str">
+        <v>CFO</v>
+      </c>
+      <c r="I22" t="str">
+        <v>CFO</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K22" t="str">
+        <v>France</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="N22" t="str">
+        <v>CC-SGA-001</v>
+      </c>
+      <c r="O22" t="str">
+        <v>SGA</v>
+      </c>
+      <c r="P22" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="R22" t="str">
+        <v>Levier identifié</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>1.68</v>
+      </c>
+      <c r="U22">
+        <v>1.5</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0.18</v>
+      </c>
+      <c r="Y22">
+        <v>0.12</v>
+      </c>
+      <c r="Z22">
+        <v>0.03</v>
+      </c>
+      <c r="AA22" t="str">
+        <v>AC-020:FS;AC-016:FF</v>
+      </c>
+      <c r="AB22" t="str">
+        <v>Levier de démo généré (réorganisation &amp; effectifs, France).</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>AC-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Supply Chain &amp; Logistique</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Programme qualité France</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Achats &amp; Supply Chain</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="G23" t="str">
+        <v>SA</v>
+      </c>
+      <c r="H23" t="str">
+        <v>CMO</v>
+      </c>
+      <c r="I23" t="str">
+        <v>CMO</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="N23" t="str">
+        <v>CC-OPS-001</v>
+      </c>
+      <c r="O23" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P23" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>2026-12-28</v>
+      </c>
+      <c r="R23" t="str">
+        <v>Business case validé</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>2.18</v>
+      </c>
+      <c r="U23">
+        <v>1.95</v>
+      </c>
+      <c r="V23">
+        <v>-3</v>
+      </c>
+      <c r="W23">
+        <v>21</v>
+      </c>
+      <c r="X23">
+        <v>0.23</v>
+      </c>
+      <c r="Y23">
+        <v>0.16</v>
+      </c>
+      <c r="Z23">
+        <v>0.04</v>
+      </c>
+      <c r="AA23" t="str">
+        <v/>
+      </c>
+      <c r="AB23" t="str">
+        <v>Levier de démo généré (supply chain &amp; logistique, Germany).</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>AC-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Digitalisation &amp; Automatisation</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Renégociation baux Allemagne</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Finance &amp; Contrôle de gestion</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>Henrik Dahl</v>
+      </c>
+      <c r="G24" t="str">
+        <v>HD</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Directeur Commercial</v>
+      </c>
+      <c r="I24" t="str">
+        <v>DC</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="N24" t="str">
+        <v>CC-GA-002</v>
+      </c>
+      <c r="O24" t="str">
+        <v>GA</v>
+      </c>
+      <c r="P24" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="R24" t="str">
+        <v>Implémentation planifiée</v>
+      </c>
+      <c r="S24">
+        <v>10</v>
+      </c>
+      <c r="T24">
+        <v>2.69</v>
+      </c>
+      <c r="U24">
+        <v>2.4</v>
+      </c>
+      <c r="V24">
+        <v>-4</v>
+      </c>
+      <c r="W24">
+        <v>32</v>
+      </c>
+      <c r="X24">
+        <v>0.29</v>
+      </c>
+      <c r="Y24">
+        <v>0.19</v>
+      </c>
+      <c r="Z24">
+        <v>0.05</v>
+      </c>
+      <c r="AA24" t="str">
+        <v>AC-022:FF</v>
+      </c>
+      <c r="AB24" t="str">
+        <v>Levier de démo généré (digitalisation &amp; automatisation, Spain).</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>AC-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Réorganisation &amp; Effectifs</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Centralisation achats indirects Espagne</v>
+      </c>
+      <c r="D25" t="str">
+        <v>RH &amp; Organisation</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>Camille Vasseur</v>
+      </c>
+      <c r="G25" t="str">
+        <v>CV</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Directrice RH</v>
+      </c>
+      <c r="I25" t="str">
+        <v>DRH</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="K25" t="str">
+        <v>USA</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="M25" t="str">
+        <v>HR</v>
+      </c>
+      <c r="N25" t="str">
+        <v>CC-GA-002</v>
+      </c>
+      <c r="O25" t="str">
+        <v>GA</v>
+      </c>
+      <c r="P25" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="R25" t="str">
+        <v>En cours d'exécution</v>
+      </c>
+      <c r="S25">
+        <v>75</v>
+      </c>
+      <c r="T25">
+        <v>3.19</v>
+      </c>
+      <c r="U25">
+        <v>2.85</v>
+      </c>
+      <c r="V25">
+        <v>-5</v>
+      </c>
+      <c r="W25">
+        <v>45</v>
+      </c>
+      <c r="X25">
+        <v>0.34</v>
+      </c>
+      <c r="Y25">
+        <v>0.23</v>
+      </c>
+      <c r="Z25">
+        <v>0.06</v>
+      </c>
+      <c r="AA25" t="str">
+        <v>AC-022:SF</v>
+      </c>
+      <c r="AB25" t="str">
+        <v>Levier de démo généré (réorganisation &amp; effectifs, USA).</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>AC-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Sourcing &amp; Achats</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Digitalisation reporting US</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Achats &amp; Supply Chain</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>Isabelle Roy</v>
+      </c>
+      <c r="G26" t="str">
+        <v>IR</v>
+      </c>
+      <c r="H26" t="str">
+        <v>CEO Office</v>
+      </c>
+      <c r="I26" t="str">
+        <v>CEO</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K26" t="str">
+        <v>France</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="N26" t="str">
+        <v>CC-PROC-001</v>
+      </c>
+      <c r="O26" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P26" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="R26" t="str">
+        <v>Valeur réalisée</v>
+      </c>
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
+        <v>3.7</v>
+      </c>
+      <c r="U26">
+        <v>3.3</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0.4</v>
+      </c>
+      <c r="Y26">
+        <v>0.26</v>
+      </c>
+      <c r="Z26">
+        <v>0.07</v>
+      </c>
+      <c r="AA26" t="str">
+        <v>AC-020:FF</v>
+      </c>
+      <c r="AB26" t="str">
+        <v>Levier de démo généré (sourcing &amp; achats, France).</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>AC-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Excellence Opérationnelle</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Rationalisation gamme EMEA</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Excellence Opérationnelle</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>Thomas Petit</v>
+      </c>
+      <c r="G27" t="str">
+        <v>TP</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Directeur Industriel</v>
+      </c>
+      <c r="I27" t="str">
+        <v>DI</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="N27" t="str">
+        <v>CC-OPS-001</v>
+      </c>
+      <c r="O27" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P27" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>2026-12-28</v>
+      </c>
+      <c r="R27" t="str">
+        <v>Levier identifié</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>4.2</v>
+      </c>
+      <c r="U27">
+        <v>3.75</v>
+      </c>
+      <c r="V27">
+        <v>-2</v>
+      </c>
+      <c r="W27">
+        <v>14</v>
+      </c>
+      <c r="X27">
+        <v>0.45</v>
+      </c>
+      <c r="Y27">
+        <v>0.3</v>
+      </c>
+      <c r="Z27">
+        <v>0.08</v>
+      </c>
+      <c r="AA27" t="str">
+        <v>AC-024:SS</v>
+      </c>
+      <c r="AB27" t="str">
+        <v>Levier de démo généré (excellence opérationnelle, Germany).</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>AC-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Digitalisation &amp; Automatisation</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Mutualisation flotte Nord</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Digital &amp; IT</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>Claire Fontaine</v>
+      </c>
+      <c r="G28" t="str">
+        <v>CF</v>
+      </c>
+      <c r="H28" t="str">
+        <v>CFO</v>
+      </c>
+      <c r="I28" t="str">
+        <v>CFO</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Acme Iberia SL</v>
+      </c>
+      <c r="M28" t="str">
+        <v>IT</v>
+      </c>
+      <c r="N28" t="str">
+        <v>CC-GA-001</v>
+      </c>
+      <c r="O28" t="str">
+        <v>GA</v>
+      </c>
+      <c r="P28" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="R28" t="str">
+        <v>Business case validé</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>4.7</v>
+      </c>
+      <c r="U28">
+        <v>4.2</v>
+      </c>
+      <c r="V28">
+        <v>-3</v>
+      </c>
+      <c r="W28">
+        <v>24</v>
+      </c>
+      <c r="X28">
+        <v>0.5</v>
+      </c>
+      <c r="Y28">
+        <v>0.34</v>
+      </c>
+      <c r="Z28">
+        <v>0.08</v>
+      </c>
+      <c r="AA28" t="str">
+        <v>AC-026:FF</v>
+      </c>
+      <c r="AB28" t="str">
+        <v>Levier de démo généré (digitalisation &amp; automatisation, Spain).</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>AC-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Pricing &amp; Revenue Management</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Automatisation support client Sud</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Marketing &amp; Ventes</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>Nadia Klein</v>
+      </c>
+      <c r="G29" t="str">
+        <v>NK</v>
+      </c>
+      <c r="H29" t="str">
+        <v>CMO</v>
+      </c>
+      <c r="I29" t="str">
+        <v>CMO</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Americas</v>
+      </c>
+      <c r="K29" t="str">
+        <v>USA</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Acme USA Inc.</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="N29" t="str">
+        <v>CC-SGA-002</v>
+      </c>
+      <c r="O29" t="str">
+        <v>REV</v>
+      </c>
+      <c r="P29" t="str">
+        <v>2026-08-01</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>2027-04-28</v>
+      </c>
+      <c r="R29" t="str">
+        <v>Implémentation planifiée</v>
+      </c>
+      <c r="S29">
+        <v>5</v>
+      </c>
+      <c r="T29">
+        <v>0.67</v>
+      </c>
+      <c r="U29">
+        <v>0.6</v>
+      </c>
+      <c r="V29">
+        <v>-4</v>
+      </c>
+      <c r="W29">
+        <v>36</v>
+      </c>
+      <c r="X29">
+        <v>0.07</v>
+      </c>
+      <c r="Y29">
+        <v>0.05</v>
+      </c>
+      <c r="Z29">
+        <v>0.01</v>
+      </c>
+      <c r="AA29" t="str">
+        <v/>
+      </c>
+      <c r="AB29" t="str">
+        <v>Levier de démo généré (pricing &amp; revenue management, USA).</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>AC-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Réorganisation &amp; Effectifs</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Optimisation stocks Groupe</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Marketing &amp; Ventes</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>Elena Ruiz</v>
+      </c>
+      <c r="G30" t="str">
+        <v>ER</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Directeur Commercial</v>
+      </c>
+      <c r="I30" t="str">
+        <v>DC</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K30" t="str">
+        <v>France</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Acme France SAS</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="N30" t="str">
+        <v>CC-SGA-001</v>
+      </c>
+      <c r="O30" t="str">
+        <v>SGA</v>
+      </c>
+      <c r="P30" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>2027-06-28</v>
+      </c>
+      <c r="R30" t="str">
+        <v>En cours d'exécution</v>
+      </c>
+      <c r="S30">
+        <v>65</v>
+      </c>
+      <c r="T30">
+        <v>1.18</v>
+      </c>
+      <c r="U30">
+        <v>1.05</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0.13</v>
+      </c>
+      <c r="Y30">
+        <v>0.08</v>
+      </c>
+      <c r="Z30">
+        <v>0.02</v>
+      </c>
+      <c r="AA30" t="str">
+        <v>AC-028:FS;AC-024:FF</v>
+      </c>
+      <c r="AB30" t="str">
+        <v>Levier de démo généré (réorganisation &amp; effectifs, France).</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>AC-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Supply Chain &amp; Logistique</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Réorganisation service client Retail</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Achats &amp; Supply Chain</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>Ryan Cole</v>
+      </c>
+      <c r="G31" t="str">
+        <v>RC</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Directrice RH</v>
+      </c>
+      <c r="I31" t="str">
+        <v>DRH</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Europe</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Acme Deutschland GmbH</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Supply Chain</v>
+      </c>
+      <c r="N31" t="str">
+        <v>CC-OPS-001</v>
+      </c>
+      <c r="O31" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="P31" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>2027-08-28</v>
+      </c>
+      <c r="R31" t="str">
+        <v>Valeur réalisée</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
+        <v>1.68</v>
+      </c>
+      <c r="U31">
+        <v>1.5</v>
+      </c>
+      <c r="V31">
+        <v>-6</v>
+      </c>
+      <c r="W31">
+        <v>42</v>
+      </c>
+      <c r="X31">
+        <v>0.18</v>
+      </c>
+      <c r="Y31">
+        <v>0.12</v>
+      </c>
+      <c r="Z31">
+        <v>0.03</v>
+      </c>
+      <c r="AA31" t="str">
+        <v>AC-028:SS</v>
+      </c>
+      <c r="AB31" t="str">
+        <v>Levier de démo généré (supply chain &amp; logistique, Germany).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB31"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/demo/leviers_demo.xlsx
+++ b/demo/leviers_demo.xlsx
@@ -540,7 +540,7 @@
         <v>2026-06-28</v>
       </c>
       <c r="R2" t="str">
-        <v>Levier identifié</v>
+        <v>Identifié</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>2026-08-28</v>
       </c>
       <c r="R3" t="str">
-        <v>Business case validé</v>
+        <v>Validé</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -712,7 +712,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="R4" t="str">
-        <v>Implémentation planifiée</v>
+        <v>Planifié</v>
       </c>
       <c r="S4">
         <v>15</v>
@@ -798,7 +798,7 @@
         <v>2026-12-28</v>
       </c>
       <c r="R5" t="str">
-        <v>En cours d'exécution</v>
+        <v>Exécuté</v>
       </c>
       <c r="S5">
         <v>55</v>
@@ -884,7 +884,7 @@
         <v>2027-02-28</v>
       </c>
       <c r="R6" t="str">
-        <v>Valeur réalisée</v>
+        <v>Réalisé</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -970,7 +970,7 @@
         <v>2027-04-28</v>
       </c>
       <c r="R7" t="str">
-        <v>Levier identifié</v>
+        <v>Identifié</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>2027-06-28</v>
       </c>
       <c r="R8" t="str">
-        <v>Business case validé</v>
+        <v>Validé</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1142,7 +1142,7 @@
         <v>2027-08-28</v>
       </c>
       <c r="R9" t="str">
-        <v>Implémentation planifiée</v>
+        <v>Planifié</v>
       </c>
       <c r="S9">
         <v>10</v>
@@ -1228,7 +1228,7 @@
         <v>2027-02-28</v>
       </c>
       <c r="R10" t="str">
-        <v>En cours d'exécution</v>
+        <v>Exécuté</v>
       </c>
       <c r="S10">
         <v>45</v>
@@ -1314,7 +1314,7 @@
         <v>2027-04-28</v>
       </c>
       <c r="R11" t="str">
-        <v>Valeur réalisée</v>
+        <v>Réalisé</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -1400,7 +1400,7 @@
         <v>2026-08-28</v>
       </c>
       <c r="R12" t="str">
-        <v>Levier identifié</v>
+        <v>Identifié</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="R13" t="str">
-        <v>Business case validé</v>
+        <v>Validé</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1572,7 +1572,7 @@
         <v>2026-12-28</v>
       </c>
       <c r="R14" t="str">
-        <v>Implémentation planifiée</v>
+        <v>Planifié</v>
       </c>
       <c r="S14">
         <v>5</v>
@@ -1658,7 +1658,7 @@
         <v>2027-02-28</v>
       </c>
       <c r="R15" t="str">
-        <v>En cours d'exécution</v>
+        <v>Exécuté</v>
       </c>
       <c r="S15">
         <v>35</v>
@@ -1744,7 +1744,7 @@
         <v>2027-04-28</v>
       </c>
       <c r="R16" t="str">
-        <v>Valeur réalisée</v>
+        <v>Réalisé</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -1830,7 +1830,7 @@
         <v>2027-06-28</v>
       </c>
       <c r="R17" t="str">
-        <v>Levier identifié</v>
+        <v>Identifié</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         <v>2026-12-28</v>
       </c>
       <c r="R18" t="str">
-        <v>Business case validé</v>
+        <v>Validé</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2002,7 +2002,7 @@
         <v>2027-02-28</v>
       </c>
       <c r="R19" t="str">
-        <v>Implémentation planifiée</v>
+        <v>Planifié</v>
       </c>
       <c r="S19">
         <v>15</v>
@@ -2088,7 +2088,7 @@
         <v>2027-04-28</v>
       </c>
       <c r="R20" t="str">
-        <v>En cours d'exécution</v>
+        <v>Exécuté</v>
       </c>
       <c r="S20">
         <v>25</v>
@@ -2174,7 +2174,7 @@
         <v>2027-06-28</v>
       </c>
       <c r="R21" t="str">
-        <v>Valeur réalisée</v>
+        <v>Réalisé</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -2260,7 +2260,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="R22" t="str">
-        <v>Levier identifié</v>
+        <v>Identifié</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -2346,7 +2346,7 @@
         <v>2026-12-28</v>
       </c>
       <c r="R23" t="str">
-        <v>Business case validé</v>
+        <v>Validé</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>2027-02-28</v>
       </c>
       <c r="R24" t="str">
-        <v>Implémentation planifiée</v>
+        <v>Planifié</v>
       </c>
       <c r="S24">
         <v>10</v>
@@ -2518,7 +2518,7 @@
         <v>2027-04-28</v>
       </c>
       <c r="R25" t="str">
-        <v>En cours d'exécution</v>
+        <v>Exécuté</v>
       </c>
       <c r="S25">
         <v>75</v>
@@ -2604,7 +2604,7 @@
         <v>2026-10-28</v>
       </c>
       <c r="R26" t="str">
-        <v>Valeur réalisée</v>
+        <v>Réalisé</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -2690,7 +2690,7 @@
         <v>2026-12-28</v>
       </c>
       <c r="R27" t="str">
-        <v>Levier identifié</v>
+        <v>Identifié</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>2027-02-28</v>
       </c>
       <c r="R28" t="str">
-        <v>Business case validé</v>
+        <v>Validé</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>2027-04-28</v>
       </c>
       <c r="R29" t="str">
-        <v>Implémentation planifiée</v>
+        <v>Planifié</v>
       </c>
       <c r="S29">
         <v>5</v>
@@ -2948,7 +2948,7 @@
         <v>2027-06-28</v>
       </c>
       <c r="R30" t="str">
-        <v>En cours d'exécution</v>
+        <v>Exécuté</v>
       </c>
       <c r="S30">
         <v>65</v>
@@ -3034,7 +3034,7 @@
         <v>2027-08-28</v>
       </c>
       <c r="R31" t="str">
-        <v>Valeur réalisée</v>
+        <v>Réalisé</v>
       </c>
       <c r="S31">
         <v>100</v>
